--- a/data/Data_Forgot_Password.xlsx
+++ b/data/Data_Forgot_Password.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="6900"/>
+    <workbookView windowWidth="20490" windowHeight="7620"/>
   </bookViews>
   <sheets>
     <sheet name="Data_Forgot_Password" sheetId="1" r:id="rId1"/>
@@ -27,9 +27,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>email</t>
+  </si>
+  <si>
+    <t>type</t>
   </si>
   <si>
     <t>expected</t>
@@ -38,10 +41,16 @@
     <t>lethithom123</t>
   </si>
   <si>
+    <t>invalid</t>
+  </si>
+  <si>
     <t>please include an '@' in the email address. 'lethithom123' is missing an '@'.</t>
   </si>
   <si>
     <t>test123@thom.com</t>
+  </si>
+  <si>
+    <t>not_exist</t>
   </si>
   <si>
     <t>Không tìm thấy tài khoản nào với email này.</t>
@@ -57,13 +66,18 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -404,12 +418,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -530,139 +559,142 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -677,7 +709,7 @@
     <cellStyle name="Note" xfId="8" builtinId="10"/>
     <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
     <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
     <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
     <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
     <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
@@ -1197,35 +1229,45 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultColWidth="10.2857142857143" defaultRowHeight="15" outlineLevelRow="2" outlineLevelCol="1"/>
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultColWidth="10.2857142857143" defaultRowHeight="15" outlineLevelRow="2" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="24.4285714285714" customWidth="1"/>
-    <col min="2" max="2" width="65.8571428571429" customWidth="1"/>
+    <col min="2" max="2" width="16.7142857142857" customWidth="1"/>
+    <col min="3" max="3" width="74.5714285714286" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" t="s">
+    <row r="1" ht="16.5" spans="1:3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
+    </row>
+    <row r="2" ht="16.5" spans="1:3">
+      <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" t="s">
+      <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C2" s="1" t="s">
         <v>5</v>
+      </c>
+    </row>
+    <row r="3" ht="16.5" spans="1:3">
+      <c r="A3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
